--- a/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=01/M10+_device01_10-13-2024 15:08:50.xlsx
+++ b/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=01/M10+_device01_10-13-2024 15:08:50.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Downloads/M10+_device01_10-13-2024 15:08:"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Developer/Personal/Trellis Air Quality/trellis-aq/data/Format=XLSX/Model=M10+/Floor=2/Location=Unit 210/Device=01/M10+_device01_10-13-2024 15:08:"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAB4D1D-B3AB-CE4F-9B8C-BAA7E54132E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB73F76-4DB0-9440-A3DD-C9E31334B91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="880" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10620" yWindow="2280" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NO." sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="578">
   <si>
     <t>NO.</t>
   </si>
@@ -1352,12 +1352,6 @@
   </si>
   <si>
     <t>5.4</t>
-  </si>
-  <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>2024-10-13 15:00:00(+08:00)</t>
   </si>
   <si>
     <t>AQI</t>
@@ -2111,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H169"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
@@ -2135,19 +2129,19 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2164,13 +2158,13 @@
         <v>171</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>177</v>
@@ -2190,13 +2184,13 @@
         <v>185</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>144</v>
@@ -2216,13 +2210,13 @@
         <v>180</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>95</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>166</v>
@@ -2242,13 +2236,13 @@
         <v>174</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>174</v>
@@ -2268,13 +2262,13 @@
         <v>171</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>64</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>177</v>
@@ -2294,13 +2288,13 @@
         <v>171</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>84</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>177</v>
@@ -2320,13 +2314,13 @@
         <v>171</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>95</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>177</v>
@@ -2346,13 +2340,13 @@
         <v>171</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>177</v>
@@ -2372,13 +2366,13 @@
         <v>169</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>177</v>
@@ -2398,13 +2392,13 @@
         <v>163</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>177</v>
@@ -2424,13 +2418,13 @@
         <v>153</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>177</v>
@@ -2450,13 +2444,13 @@
         <v>150</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>177</v>
@@ -2476,13 +2470,13 @@
         <v>130</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>177</v>
@@ -2502,13 +2496,13 @@
         <v>78</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>177</v>
@@ -2528,13 +2522,13 @@
         <v>70</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>177</v>
@@ -2554,13 +2548,13 @@
         <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>177</v>
@@ -2580,13 +2574,13 @@
         <v>95</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>174</v>
@@ -2606,13 +2600,13 @@
         <v>111</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>177</v>
@@ -2632,13 +2626,13 @@
         <v>200</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>174</v>
@@ -2658,13 +2652,13 @@
         <v>220</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>144</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>177</v>
@@ -2684,13 +2678,13 @@
         <v>220</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>174</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>174</v>
@@ -2710,13 +2704,13 @@
         <v>214</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>187</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>174</v>
@@ -2736,13 +2730,13 @@
         <v>232</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>336</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>174</v>
@@ -2762,13 +2756,13 @@
         <v>195</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>174</v>
@@ -2788,13 +2782,13 @@
         <v>185</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>185</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>174</v>
@@ -2814,13 +2808,13 @@
         <v>163</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>174</v>
@@ -2840,13 +2834,13 @@
         <v>158</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>171</v>
@@ -2866,13 +2860,13 @@
         <v>133</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>171</v>
@@ -2892,13 +2886,13 @@
         <v>125</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>174</v>
@@ -2918,13 +2912,13 @@
         <v>127</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>174</v>
@@ -2944,13 +2938,13 @@
         <v>144</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>174</v>
@@ -2970,13 +2964,13 @@
         <v>144</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>174</v>
@@ -2996,13 +2990,13 @@
         <v>138</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>174</v>
@@ -3022,13 +3016,13 @@
         <v>113</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>174</v>
@@ -3048,13 +3042,13 @@
         <v>113</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>174</v>
@@ -3074,13 +3068,13 @@
         <v>113</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>174</v>
@@ -3100,13 +3094,13 @@
         <v>113</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H38" s="1" t="s">
         <v>174</v>
@@ -3126,13 +3120,13 @@
         <v>116</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>174</v>
@@ -3152,13 +3146,13 @@
         <v>116</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>174</v>
@@ -3178,13 +3172,13 @@
         <v>116</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>171</v>
@@ -3204,13 +3198,13 @@
         <v>101</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>171</v>
@@ -3230,13 +3224,13 @@
         <v>98</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>174</v>
@@ -3256,13 +3250,13 @@
         <v>105</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>141</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>171</v>
@@ -3282,13 +3276,13 @@
         <v>113</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>171</v>
@@ -3308,13 +3302,13 @@
         <v>171</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>171</v>
@@ -3334,13 +3328,13 @@
         <v>160</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>169</v>
@@ -3360,13 +3354,13 @@
         <v>147</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>180</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>169</v>
@@ -3386,13 +3380,13 @@
         <v>144</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>169</v>
@@ -3412,13 +3406,13 @@
         <v>156</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>271</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>169</v>
@@ -3438,13 +3432,13 @@
         <v>147</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>275</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>169</v>
@@ -3464,13 +3458,13 @@
         <v>136</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>169</v>
@@ -3490,13 +3484,13 @@
         <v>130</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>169</v>
@@ -3516,13 +3510,13 @@
         <v>103</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H54" s="1" t="s">
         <v>169</v>
@@ -3542,13 +3536,13 @@
         <v>105</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H55" s="1" t="s">
         <v>169</v>
@@ -3568,13 +3562,13 @@
         <v>138</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>171</v>
@@ -3594,13 +3588,13 @@
         <v>169</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>171</v>
@@ -3620,13 +3614,13 @@
         <v>177</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H58" s="1" t="s">
         <v>171</v>
@@ -3646,13 +3640,13 @@
         <v>174</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H59" s="1" t="s">
         <v>171</v>
@@ -3672,13 +3666,13 @@
         <v>163</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>171</v>
@@ -3698,13 +3692,13 @@
         <v>163</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H61" s="1" t="s">
         <v>171</v>
@@ -3724,13 +3718,13 @@
         <v>166</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H62" s="1" t="s">
         <v>171</v>
@@ -3750,13 +3744,13 @@
         <v>158</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>171</v>
@@ -3776,13 +3770,13 @@
         <v>160</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>169</v>
@@ -3802,13 +3796,13 @@
         <v>153</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>169</v>
@@ -3828,13 +3822,13 @@
         <v>158</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>169</v>
@@ -3854,13 +3848,13 @@
         <v>160</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H67" s="1" t="s">
         <v>166</v>
@@ -3880,13 +3874,13 @@
         <v>180</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>166</v>
@@ -3906,13 +3900,13 @@
         <v>180</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>169</v>
@@ -3932,13 +3926,13 @@
         <v>169</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>150</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>166</v>
@@ -3958,13 +3952,13 @@
         <v>163</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>156</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>166</v>
@@ -3984,13 +3978,13 @@
         <v>163</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>166</v>
@@ -4010,13 +4004,13 @@
         <v>150</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>166</v>
@@ -4036,13 +4030,13 @@
         <v>156</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>166</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>163</v>
@@ -4062,13 +4056,13 @@
         <v>153</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>277</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>166</v>
@@ -4088,13 +4082,13 @@
         <v>239</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>279</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>166</v>
@@ -4114,13 +4108,13 @@
         <v>190</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>166</v>
@@ -4140,13 +4134,13 @@
         <v>200</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>166</v>
@@ -4166,13 +4160,13 @@
         <v>203</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>166</v>
@@ -4192,13 +4186,13 @@
         <v>187</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H80" s="1" t="s">
         <v>169</v>
@@ -4218,13 +4212,13 @@
         <v>183</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>169</v>
@@ -4244,13 +4238,13 @@
         <v>166</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>169</v>
@@ -4270,13 +4264,13 @@
         <v>150</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>169</v>
@@ -4296,13 +4290,13 @@
         <v>147</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>127</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>169</v>
@@ -4322,13 +4316,13 @@
         <v>147</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>169</v>
@@ -4348,13 +4342,13 @@
         <v>150</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>169</v>
@@ -4374,13 +4368,13 @@
         <v>156</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H87" s="1" t="s">
         <v>169</v>
@@ -4400,13 +4394,13 @@
         <v>158</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>169</v>
@@ -4426,13 +4420,13 @@
         <v>158</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>138</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>166</v>
@@ -4452,13 +4446,13 @@
         <v>160</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>166</v>
@@ -4478,13 +4472,13 @@
         <v>214</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>166</v>
@@ -4504,13 +4498,13 @@
         <v>198</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>166</v>
@@ -4530,13 +4524,13 @@
         <v>183</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>141</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>166</v>
@@ -4556,13 +4550,13 @@
         <v>180</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>166</v>
@@ -4582,13 +4576,13 @@
         <v>169</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>190</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>163</v>
@@ -4608,13 +4602,13 @@
         <v>160</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>183</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>163</v>
@@ -4634,13 +4628,13 @@
         <v>156</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>177</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>163</v>
@@ -4660,13 +4654,13 @@
         <v>150</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>325</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>163</v>
@@ -4686,13 +4680,13 @@
         <v>144</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>163</v>
@@ -4712,13 +4706,13 @@
         <v>133</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>163</v>
@@ -4738,13 +4732,13 @@
         <v>133</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>163</v>
@@ -4764,13 +4758,13 @@
         <v>166</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>166</v>
@@ -4790,13 +4784,13 @@
         <v>171</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>166</v>
@@ -4816,13 +4810,13 @@
         <v>177</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>169</v>
@@ -4842,13 +4836,13 @@
         <v>185</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>171</v>
@@ -4868,13 +4862,13 @@
         <v>183</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>171</v>
@@ -4894,13 +4888,13 @@
         <v>163</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>171</v>
@@ -4920,13 +4914,13 @@
         <v>153</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>171</v>
@@ -4946,13 +4940,13 @@
         <v>147</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>103</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>171</v>
@@ -4972,13 +4966,13 @@
         <v>136</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>174</v>
@@ -4998,13 +4992,13 @@
         <v>130</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>171</v>
@@ -5024,13 +5018,13 @@
         <v>122</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>171</v>
@@ -5050,13 +5044,13 @@
         <v>125</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>171</v>
@@ -5076,13 +5070,13 @@
         <v>136</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>171</v>
@@ -5102,13 +5096,13 @@
         <v>147</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>171</v>
@@ -5128,13 +5122,13 @@
         <v>239</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>133</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>171</v>
@@ -5154,13 +5148,13 @@
         <v>195</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>141</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>169</v>
@@ -5180,13 +5174,13 @@
         <v>187</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>166</v>
@@ -5206,13 +5200,13 @@
         <v>177</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>183</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>163</v>
@@ -5232,13 +5226,13 @@
         <v>195</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>187</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>163</v>
@@ -5258,13 +5252,13 @@
         <v>169</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>166</v>
@@ -5284,13 +5278,13 @@
         <v>169</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>422</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>166</v>
@@ -5310,13 +5304,13 @@
         <v>166</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>166</v>
@@ -5336,13 +5330,13 @@
         <v>163</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>130</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>166</v>
@@ -5362,13 +5356,13 @@
         <v>163</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>169</v>
@@ -5388,13 +5382,13 @@
         <v>174</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>169</v>
@@ -5414,13 +5408,13 @@
         <v>226</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>171</v>
@@ -5440,13 +5434,13 @@
         <v>237</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>169</v>
@@ -5466,13 +5460,13 @@
         <v>235</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>169</v>
@@ -5492,13 +5486,13 @@
         <v>226</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>169</v>
@@ -5518,13 +5512,13 @@
         <v>203</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>105</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>169</v>
@@ -5544,13 +5538,13 @@
         <v>171</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>169</v>
@@ -5570,13 +5564,13 @@
         <v>150</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>169</v>
@@ -5596,13 +5590,13 @@
         <v>144</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>169</v>
@@ -5622,13 +5616,13 @@
         <v>147</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>113</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H135" s="1" t="s">
         <v>169</v>
@@ -5648,13 +5642,13 @@
         <v>153</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>169</v>
@@ -5674,13 +5668,13 @@
         <v>158</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H137" s="1" t="s">
         <v>166</v>
@@ -5700,13 +5694,13 @@
         <v>158</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>166</v>
@@ -5726,13 +5720,13 @@
         <v>158</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>169</v>
@@ -5752,13 +5746,13 @@
         <v>166</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H140" s="1" t="s">
         <v>166</v>
@@ -5778,13 +5772,13 @@
         <v>171</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H141" s="1" t="s">
         <v>166</v>
@@ -5804,13 +5798,13 @@
         <v>169</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>166</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>163</v>
@@ -5830,13 +5824,13 @@
         <v>163</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>166</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>160</v>
@@ -5856,13 +5850,13 @@
         <v>160</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>183</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="H144" s="1" t="s">
         <v>160</v>
@@ -5882,13 +5876,13 @@
         <v>160</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>169</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>160</v>
@@ -5908,13 +5902,13 @@
         <v>166</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>163</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H146" s="1" t="s">
         <v>160</v>
@@ -5934,13 +5928,13 @@
         <v>171</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H147" s="1" t="s">
         <v>163</v>
@@ -5960,13 +5954,13 @@
         <v>166</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>153</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="H148" s="1" t="s">
         <v>169</v>
@@ -5986,13 +5980,13 @@
         <v>158</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>171</v>
@@ -6012,13 +6006,13 @@
         <v>158</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H150" s="1" t="s">
         <v>171</v>
@@ -6038,13 +6032,13 @@
         <v>229</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H151" s="1" t="s">
         <v>171</v>
@@ -6064,13 +6058,13 @@
         <v>214</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H152" s="1" t="s">
         <v>171</v>
@@ -6090,13 +6084,13 @@
         <v>177</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>174</v>
@@ -6116,13 +6110,13 @@
         <v>163</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>108</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>171</v>
@@ -6142,13 +6136,13 @@
         <v>119</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>111</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>171</v>
@@ -6168,13 +6162,13 @@
         <v>93</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>169</v>
@@ -6194,13 +6188,13 @@
         <v>73</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>125</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="H157" s="1" t="s">
         <v>169</v>
@@ -6220,13 +6214,13 @@
         <v>64</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>166</v>
@@ -6246,13 +6240,13 @@
         <v>64</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H159" s="1" t="s">
         <v>163</v>
@@ -6272,13 +6266,13 @@
         <v>64</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>116</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>160</v>
@@ -6298,13 +6292,13 @@
         <v>73</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>158</v>
@@ -6324,13 +6318,13 @@
         <v>130</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>122</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>158</v>
@@ -6350,13 +6344,13 @@
         <v>133</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>119</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H163" s="1" t="s">
         <v>158</v>
@@ -6376,13 +6370,13 @@
         <v>101</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>158</v>
@@ -6402,13 +6396,13 @@
         <v>93</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>136</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>156</v>
@@ -6428,13 +6422,13 @@
         <v>87</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>147</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>156</v>
@@ -6454,13 +6448,13 @@
         <v>87</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>160</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>156</v>
@@ -6480,41 +6474,15 @@
         <v>87</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="H168" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A169" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="G169" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="H169" s="1" t="s">
         <v>156</v>
       </c>
     </row>
